--- a/assets/system_config.xlsx
+++ b/assets/system_config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\P.Project\NodeJS\F.Factory\AssetManage\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\5.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334B67B2-1721-4394-9CF7-BEAA3FB4D6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D5F0DF-DD12-47B9-8ECB-DE24BD362F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="69">
   <si>
     <t>id</t>
   </si>
@@ -194,9 +194,6 @@
     <t>1st Floor</t>
   </si>
   <si>
-    <t>assets/Floor1.png</t>
-  </si>
-  <si>
     <t>assets/floor_1_data.xlsx</t>
   </si>
   <si>
@@ -225,6 +222,18 @@
   </si>
   <si>
     <t>assets/floor_3_data.xlsx</t>
+  </si>
+  <si>
+    <t>assets/2nd Floor.png</t>
+  </si>
+  <si>
+    <t>assets/1st Floor-B.png</t>
+  </si>
+  <si>
+    <t>assets/3rd Floor-B.png</t>
+  </si>
+  <si>
+    <t>assets/4th Floor-B.png</t>
   </si>
 </sst>
 </file>
@@ -854,52 +863,52 @@
         <v>54</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/assets/system_config.xlsx
+++ b/assets/system_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\5.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D5F0DF-DD12-47B9-8ECB-DE24BD362F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF6DE29-616F-4BAA-8950-F5EE9949DE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22125" yWindow="2370" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Layers" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="77">
   <si>
     <t>id</t>
   </si>
@@ -234,6 +234,30 @@
   </si>
   <si>
     <t>assets/4th Floor-B.png</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>house</t>
+  </si>
+  <si>
+    <t>camera</t>
+  </si>
+  <si>
+    <t>paper</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Paper Form</t>
+  </si>
+  <si>
+    <t>#D2B48C</t>
+  </si>
+  <si>
+    <t>note</t>
   </si>
 </sst>
 </file>
@@ -258,15 +282,21 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -285,11 +315,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -297,8 +351,34 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -519,143 +599,177 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="5.5703125" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" s="5" customFormat="1">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="E1" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="b">
+      <c r="D2" s="6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="E2" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="b">
+      <c r="D3" s="6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="b">
+      <c r="D4" s="6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="2" t="b">
+      <c r="D5" s="6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="2" t="b">
+      <c r="D6" s="6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="2" t="b">
+      <c r="D7" s="6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
+      <c r="E7" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="2" t="b">
+      <c r="D8" s="6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
+      <c r="E8" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="2" t="b">
+      <c r="D9" s="6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3"/>
+      <c r="E9" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>76</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -667,7 +781,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -688,7 +802,7 @@
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>32</v>
       </c>
     </row>
@@ -699,7 +813,7 @@
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>34</v>
       </c>
     </row>
@@ -710,7 +824,7 @@
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>36</v>
       </c>
     </row>
@@ -721,7 +835,7 @@
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>38</v>
       </c>
     </row>
@@ -732,7 +846,7 @@
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>38</v>
       </c>
     </row>
@@ -743,7 +857,7 @@
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>38</v>
       </c>
     </row>
@@ -754,7 +868,7 @@
       <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>38</v>
       </c>
     </row>
@@ -765,29 +879,29 @@
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>44</v>
       </c>
     </row>
@@ -798,7 +912,7 @@
       <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>47</v>
       </c>
     </row>
@@ -809,19 +923,30 @@
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="9" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A15" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -879,7 +1004,7 @@
       <c r="C3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -907,7 +1032,7 @@
       <c r="C5" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>63</v>
       </c>
     </row>

--- a/assets/system_config.xlsx
+++ b/assets/system_config.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="14.5703125" customWidth="1" min="1" max="1"/>
@@ -731,6 +731,31 @@
       <c r="F11" t="inlineStr">
         <is>
           <t>area</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>flow</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Flow Paths</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>#FF6600</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>flow</t>
         </is>
       </c>
     </row>

--- a/assets/system_config.xlsx
+++ b/assets/system_config.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="14.5703125" customWidth="1" min="1" max="1"/>
@@ -454,6 +454,11 @@
           <t>RenderType</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
@@ -484,6 +489,11 @@
           <t>device</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -510,6 +520,11 @@
           <t>device</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -536,6 +551,11 @@
           <t>device</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -562,6 +582,11 @@
           <t>device</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -588,6 +613,11 @@
           <t>device</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -618,6 +648,11 @@
           <t>device</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -648,6 +683,11 @@
           <t>device</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -678,6 +718,11 @@
           <t>device</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -708,6 +753,11 @@
           <t>device</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -733,6 +783,11 @@
           <t>area</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -756,6 +811,11 @@
       <c r="F12" t="inlineStr">
         <is>
           <t>flow</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Production</t>
         </is>
       </c>
     </row>

--- a/assets/system_config.xlsx
+++ b/assets/system_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5786CB-918B-41AB-A4CF-A8F8EA992B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BEBB5D6-D2E8-45D8-A667-39A68CB375A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="84">
   <si>
     <t>id</t>
   </si>
@@ -134,9 +134,6 @@
     <t>flow</t>
   </si>
   <si>
-    <t>Flow Paths</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -264,6 +261,24 @@
   </si>
   <si>
     <t>GWINS</t>
+  </si>
+  <si>
+    <t>flow_rtd</t>
+  </si>
+  <si>
+    <t>flow_pouch</t>
+  </si>
+  <si>
+    <t>Flow Pouch</t>
+  </si>
+  <si>
+    <t>Flow RTD</t>
+  </si>
+  <si>
+    <t>flow_can</t>
+  </si>
+  <si>
+    <t>Flow Can</t>
   </si>
 </sst>
 </file>
@@ -349,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -386,6 +401,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -606,17 +630,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
     <col min="2" max="2" width="21.5703125" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" style="16" customWidth="1"/>
     <col min="5" max="5" width="13" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1">
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="12.75">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -626,7 +650,7 @@
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -639,7 +663,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" ht="12.75">
       <c r="A2" s="11" t="s">
         <v>7</v>
       </c>
@@ -662,7 +686,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" ht="12.75">
       <c r="A3" s="12" t="s">
         <v>30</v>
       </c>
@@ -672,7 +696,7 @@
       <c r="C3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="12" t="b">
+      <c r="D3" s="15" t="b">
         <v>1</v>
       </c>
       <c r="E3" s="7"/>
@@ -683,7 +707,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" ht="12.75">
       <c r="A4" s="11" t="s">
         <v>23</v>
       </c>
@@ -706,7 +730,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="12.75">
       <c r="A5" s="11" t="s">
         <v>13</v>
       </c>
@@ -727,12 +751,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="12.75">
       <c r="A6" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>76</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>17</v>
@@ -748,7 +772,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" ht="12.75">
       <c r="A7" s="11" t="s">
         <v>18</v>
       </c>
@@ -771,15 +795,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" ht="12.75">
       <c r="A8" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="C8" s="11" t="s">
         <v>70</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>71</v>
       </c>
       <c r="D8" s="11" t="b">
         <v>1</v>
@@ -792,15 +816,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" ht="12.75">
       <c r="A9" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C9" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>74</v>
       </c>
       <c r="D9" s="11" t="b">
         <v>1</v>
@@ -813,7 +837,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" ht="12.75">
       <c r="A10" s="11" t="s">
         <v>26</v>
       </c>
@@ -836,17 +860,17 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" ht="12.75">
       <c r="A11" s="12" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="12" t="b">
+      <c r="D11" s="15" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="7"/>
@@ -854,6 +878,48 @@
         <v>34</v>
       </c>
       <c r="G11" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="12.75">
+      <c r="A12" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A13" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="12" t="s">
         <v>22</v>
       </c>
     </row>
@@ -872,95 +938,95 @@
   <sheetData>
     <row r="1" spans="1:3" ht="12.75">
       <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="12.75">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="12.75">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="12.75">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="12.75">
       <c r="A5" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="12.75">
       <c r="A6" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="12.75">
       <c r="A7" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="12.75">
       <c r="A8" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="12.75">
       <c r="A9" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>18</v>
@@ -971,7 +1037,7 @@
     </row>
     <row r="10" spans="1:3" ht="12.75">
       <c r="A10" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>18</v>
@@ -982,7 +1048,7 @@
     </row>
     <row r="11" spans="1:3" ht="12.75">
       <c r="A11" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>23</v>
@@ -993,7 +1059,7 @@
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1">
       <c r="A12" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>26</v>
@@ -1027,66 +1093,66 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/assets/system_config.xlsx
+++ b/assets/system_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BEBB5D6-D2E8-45D8-A667-39A68CB375A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F7E1FF-89E1-42CF-938A-9EA537413461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Layers" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>id</t>
   </si>
@@ -110,9 +110,6 @@
     <t>paper</t>
   </si>
   <si>
-    <t>Paper Form</t>
-  </si>
-  <si>
     <t>#D2B48C</t>
   </si>
   <si>
@@ -279,6 +276,33 @@
   </si>
   <si>
     <t>Flow Can</t>
+  </si>
+  <si>
+    <t>form_can</t>
+  </si>
+  <si>
+    <t>Zones (noname)</t>
+  </si>
+  <si>
+    <t>zones_noname</t>
+  </si>
+  <si>
+    <t>flow_powder</t>
+  </si>
+  <si>
+    <t>Flow Powder</t>
+  </si>
+  <si>
+    <t>form_can_1</t>
+  </si>
+  <si>
+    <t>Form Can 1</t>
+  </si>
+  <si>
+    <t>form_can_2</t>
+  </si>
+  <si>
+    <t>Form Can 2</t>
   </si>
 </sst>
 </file>
@@ -630,7 +654,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -688,43 +712,41 @@
     </row>
     <row r="3" spans="1:7" ht="12.75">
       <c r="A3" s="12" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>31</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>32</v>
       </c>
       <c r="D3" s="15" t="b">
         <v>1</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="12.75">
-      <c r="A4" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>23</v>
-      </c>
+      <c r="A4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7"/>
       <c r="F4" s="12" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>12</v>
@@ -732,34 +754,36 @@
     </row>
     <row r="5" spans="1:7" ht="12.75">
       <c r="A5" s="11" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D5" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="F5" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="12.75">
       <c r="A6" s="11" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6" s="11" t="b">
         <v>1</v>
@@ -769,25 +793,23 @@
         <v>11</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="12.75">
       <c r="A7" s="11" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D7" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>21</v>
-      </c>
+      <c r="E7" s="7"/>
       <c r="F7" s="12" t="s">
         <v>11</v>
       </c>
@@ -797,19 +819,21 @@
     </row>
     <row r="8" spans="1:7" ht="12.75">
       <c r="A8" s="11" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="D8" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="13" t="s">
+      <c r="E8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>11</v>
       </c>
       <c r="G8" s="12" t="s">
@@ -818,13 +842,13 @@
     </row>
     <row r="9" spans="1:7" ht="12.75">
       <c r="A9" s="11" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D9" s="11" t="b">
         <v>1</v>
@@ -839,21 +863,19 @@
     </row>
     <row r="10" spans="1:7" ht="12.75">
       <c r="A10" s="11" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="D10" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="12" t="s">
+      <c r="E10" s="7"/>
+      <c r="F10" s="13" t="s">
         <v>11</v>
       </c>
       <c r="G10" s="12" t="s">
@@ -861,65 +883,132 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="12.75">
-      <c r="A11" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="7"/>
+      <c r="A11" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="F11" s="12" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G11" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="12.75">
-      <c r="A12" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="7"/>
+      <c r="A12" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="F12" s="12" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G12" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A13" s="13" t="s">
-        <v>78</v>
+    <row r="13" spans="1:7" ht="12.75">
+      <c r="A13" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" s="15" t="b">
         <v>1</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G13" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="12.75">
+      <c r="A14" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="12.75">
+      <c r="A15" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A16" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="12" t="s">
         <v>22</v>
       </c>
     </row>
@@ -938,95 +1027,95 @@
   <sheetData>
     <row r="1" spans="1:3" ht="12.75">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="12.75">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="12.75">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="12.75">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="12.75">
       <c r="A5" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="12.75">
       <c r="A6" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="12.75">
       <c r="A7" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="12.75">
       <c r="A8" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="12.75">
       <c r="A9" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>18</v>
@@ -1037,7 +1126,7 @@
     </row>
     <row r="10" spans="1:3" ht="12.75">
       <c r="A10" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>18</v>
@@ -1048,7 +1137,7 @@
     </row>
     <row r="11" spans="1:3" ht="12.75">
       <c r="A11" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>23</v>
@@ -1057,12 +1146,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1">
+    <row r="12" spans="1:3" ht="12.75">
       <c r="A12" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>26</v>
@@ -1093,66 +1182,66 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/assets/system_config.xlsx
+++ b/assets/system_config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F7E1FF-89E1-42CF-938A-9EA537413461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7474BC7B-4028-4B12-900F-5D694E65A2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="97">
   <si>
     <t>id</t>
   </si>
@@ -303,13 +303,28 @@
   </si>
   <si>
     <t>Form Can 2</t>
+  </si>
+  <si>
+    <t>form_pouch_1</t>
+  </si>
+  <si>
+    <t>Form Pouch 1</t>
+  </si>
+  <si>
+    <t>form_pouch_2</t>
+  </si>
+  <si>
+    <t>Form Pouch 2</t>
+  </si>
+  <si>
+    <t>form_pouch</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -325,6 +340,11 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -654,7 +674,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -929,42 +949,46 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="12.75">
-      <c r="A13" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="7"/>
+      <c r="A13" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="F13" s="12" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="12.75">
-      <c r="A14" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="7"/>
+      <c r="A14" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="F14" s="12" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>22</v>
@@ -972,10 +996,10 @@
     </row>
     <row r="15" spans="1:7" ht="12.75">
       <c r="A15" s="12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>31</v>
@@ -991,12 +1015,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A16" s="13" t="s">
-        <v>77</v>
+    <row r="16" spans="1:7" ht="12.75">
+      <c r="A16" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>31</v>
@@ -1012,7 +1036,50 @@
         <v>22</v>
       </c>
     </row>
+    <row r="17" spans="1:7" ht="12.75">
+      <c r="A17" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A18" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1022,7 +1089,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:3" ht="12.75">
@@ -1154,6 +1221,17 @@
         <v>83</v>
       </c>
       <c r="C12" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A13" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>26</v>
       </c>
     </row>

--- a/assets/system_config.xlsx
+++ b/assets/system_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265778A5-8CF0-413C-873F-918D265D7418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63EFC230-B878-4FDC-8429-927693379239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Layers" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="100">
   <si>
     <t>id</t>
   </si>
@@ -323,7 +323,10 @@
     <t>assets/floor_4_data.xlsx</t>
   </si>
   <si>
-    <t>zones_building</t>
+    <t>Building</t>
+  </si>
+  <si>
+    <t>building</t>
   </si>
 </sst>
 </file>
@@ -785,10 +788,10 @@
     </row>
     <row r="5" spans="1:8" ht="12.75" customHeight="1">
       <c r="A5" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>19</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>16</v>

--- a/assets/system_config.xlsx
+++ b/assets/system_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63EFC230-B878-4FDC-8429-927693379239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469AF0E3-5626-4F06-A85B-EB859526C1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Layers" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="101">
   <si>
     <t>id</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>building</t>
+  </si>
+  <si>
+    <t>Popup</t>
   </si>
 </sst>
 </file>
@@ -684,7 +687,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -692,10 +695,11 @@
     <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" style="15" customWidth="1"/>
     <col min="5" max="5" width="13" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="4"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" ht="12.75" customHeight="1">
+    <row r="1" spans="1:9" s="5" customFormat="1" ht="12.75" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -717,11 +721,14 @@
       <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="12.75" customHeight="1">
+    <row r="2" spans="1:9" ht="12.75" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>8</v>
       </c>
@@ -743,8 +750,9 @@
       <c r="G2" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:9" ht="12.75" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>14</v>
       </c>
@@ -764,8 +772,9 @@
       <c r="G3" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:9" ht="12.75" customHeight="1">
       <c r="A4" s="11" t="s">
         <v>18</v>
       </c>
@@ -785,8 +794,9 @@
       <c r="G4" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:9" ht="12.75" customHeight="1">
       <c r="A5" s="11" t="s">
         <v>99</v>
       </c>
@@ -806,8 +816,9 @@
       <c r="G5" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:9" ht="12.75" customHeight="1">
       <c r="A6" s="12" t="s">
         <v>20</v>
       </c>
@@ -829,8 +840,9 @@
       <c r="G6" s="11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:9" ht="12.75" customHeight="1">
       <c r="A7" s="12" t="s">
         <v>23</v>
       </c>
@@ -850,8 +862,9 @@
       <c r="G7" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:9" ht="12.75" customHeight="1">
       <c r="A8" s="12" t="s">
         <v>27</v>
       </c>
@@ -871,8 +884,11 @@
       <c r="G8" s="11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H8" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="12.75" customHeight="1">
       <c r="A9" s="12" t="s">
         <v>31</v>
       </c>
@@ -894,8 +910,11 @@
       <c r="G9" s="11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H9" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="12.75" customHeight="1">
       <c r="A10" s="12" t="s">
         <v>35</v>
       </c>
@@ -915,8 +934,11 @@
       <c r="G10" s="11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H10" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="12.75" customHeight="1">
       <c r="A11" s="12" t="s">
         <v>38</v>
       </c>
@@ -936,9 +958,12 @@
       <c r="G11" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H11" s="7">
+        <v>1</v>
+      </c>
+      <c r="I11" s="16"/>
+    </row>
+    <row r="12" spans="1:9" ht="12.75" customHeight="1">
       <c r="A12" s="12" t="s">
         <v>41</v>
       </c>
@@ -960,9 +985,10 @@
       <c r="G12" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="16"/>
-    </row>
-    <row r="13" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H12" s="7"/>
+      <c r="I12" s="16"/>
+    </row>
+    <row r="13" spans="1:9" ht="12.75" customHeight="1">
       <c r="A13" s="12" t="s">
         <v>45</v>
       </c>
@@ -984,9 +1010,10 @@
       <c r="G13" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="16"/>
-    </row>
-    <row r="14" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H13" s="7"/>
+      <c r="I13" s="16"/>
+    </row>
+    <row r="14" spans="1:9" ht="12.75" customHeight="1">
       <c r="A14" s="12" t="s">
         <v>47</v>
       </c>
@@ -1008,9 +1035,10 @@
       <c r="G14" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H14" s="16"/>
-    </row>
-    <row r="15" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H14" s="7"/>
+      <c r="I14" s="16"/>
+    </row>
+    <row r="15" spans="1:9" ht="12.75" customHeight="1">
       <c r="A15" s="12" t="s">
         <v>49</v>
       </c>
@@ -1032,9 +1060,10 @@
       <c r="G15" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="16"/>
-    </row>
-    <row r="16" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H15" s="7"/>
+      <c r="I15" s="16"/>
+    </row>
+    <row r="16" spans="1:9" ht="12.75" customHeight="1">
       <c r="A16" s="11" t="s">
         <v>51</v>
       </c>
@@ -1054,9 +1083,10 @@
       <c r="G16" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="16"/>
-    </row>
-    <row r="17" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H16" s="7"/>
+      <c r="I16" s="16"/>
+    </row>
+    <row r="17" spans="1:9" ht="12.75" customHeight="1">
       <c r="A17" s="11" t="s">
         <v>54</v>
       </c>
@@ -1076,9 +1106,10 @@
       <c r="G17" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="16"/>
-    </row>
-    <row r="18" spans="1:8" ht="12.75" customHeight="1">
+      <c r="H17" s="7"/>
+      <c r="I17" s="16"/>
+    </row>
+    <row r="18" spans="1:9" ht="12.75" customHeight="1">
       <c r="A18" s="11" t="s">
         <v>56</v>
       </c>
@@ -1098,9 +1129,10 @@
       <c r="G18" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H18" s="16"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+      <c r="H18" s="7"/>
+      <c r="I18" s="16"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" customHeight="1">
       <c r="A19" s="12" t="s">
         <v>58</v>
       </c>
@@ -1120,7 +1152,8 @@
       <c r="G19" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H19" s="16"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
